--- a/grupos/5ALCM - Estadisticos 20241.xlsx
+++ b/grupos/5ALCM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -245,15 +245,15 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>JALAPA</t>
   </si>
   <si>
     <t>LARRACILLA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
@@ -266,15 +266,15 @@
     <t>PRADO</t>
   </si>
   <si>
+    <t>SOTO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>LUGO</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -284,13 +284,13 @@
     <t>ANETTE</t>
   </si>
   <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
     <t>JAZMIN</t>
   </si>
   <si>
     <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
   </si>
   <si>
     <t>VALERIA</t>
@@ -807,22 +807,22 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -849,7 +849,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -884,22 +884,22 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -961,22 +961,22 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1000,7 +1000,7 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1038,22 +1038,22 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1077,16 +1077,16 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>6</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1115,22 +1115,22 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1192,22 +1192,22 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1231,16 +1231,16 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>8</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1269,22 +1269,22 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1346,22 +1346,22 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1382,13 +1382,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>10</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1397,7 +1397,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1423,22 +1423,22 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1465,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1500,22 +1500,22 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1539,10 +1539,10 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1577,22 +1577,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1619,7 +1619,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1654,22 +1654,22 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1696,13 +1696,13 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>8</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1731,22 +1731,22 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1767,10 +1767,10 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -1782,7 +1782,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1808,22 +1808,22 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1856,7 +1856,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -1885,22 +1885,22 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1924,16 +1924,16 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>8</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -1962,22 +1962,22 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2001,10 +2001,10 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2039,22 +2039,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2078,16 +2078,16 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>5</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2116,22 +2116,22 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2155,7 +2155,7 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>6</v>
@@ -2193,22 +2193,22 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2235,13 +2235,13 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>6</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2270,22 +2270,22 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2309,7 +2309,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>6</v>
@@ -2318,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2347,22 +2347,22 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2424,22 +2424,22 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2463,7 +2463,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2501,22 +2501,22 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2540,10 +2540,10 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>6</v>
@@ -2578,22 +2578,22 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2626,7 +2626,7 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2655,22 +2655,22 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2694,10 +2694,10 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -2732,22 +2732,22 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2771,16 +2771,16 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>5</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2809,22 +2809,22 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2845,13 +2845,13 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>5</v>
@@ -2860,7 +2860,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2886,22 +2886,22 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2928,7 +2928,7 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -2963,22 +2963,22 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3002,7 +3002,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3011,7 +3011,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3040,22 +3040,22 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3079,10 +3079,10 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>6</v>
@@ -3117,22 +3117,22 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3194,22 +3194,22 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3236,7 +3236,7 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>6</v>
@@ -3271,22 +3271,22 @@
         <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3313,7 +3313,7 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W36">
         <v>8</v>
@@ -3348,22 +3348,22 @@
         <v>7</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3387,7 +3387,7 @@
         <v>7</v>
       </c>
       <c r="U37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>6</v>
@@ -3425,22 +3425,22 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3502,22 +3502,22 @@
         <v>10</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K39">
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3541,7 +3541,7 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V39">
         <v>10</v>
@@ -3579,22 +3579,22 @@
         <v>10</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3618,7 +3618,7 @@
         <v>10</v>
       </c>
       <c r="U40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V40">
         <v>9</v>
@@ -3656,22 +3656,22 @@
         <v>10</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K41">
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3733,22 +3733,22 @@
         <v>10</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K42">
         <v>-1</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -3772,7 +3772,7 @@
         <v>10</v>
       </c>
       <c r="U42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V42">
         <v>9</v>
@@ -3781,7 +3781,7 @@
         <v>7</v>
       </c>
       <c r="X42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y42">
         <v>10</v>
@@ -3810,22 +3810,22 @@
         <v>9</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K43">
         <v>-1</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -3846,22 +3846,22 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W43">
         <v>7</v>
       </c>
       <c r="X43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y43">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3887,22 +3887,22 @@
         <v>10</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K44">
         <v>-1</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4077,7 +4077,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -4095,7 +4095,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -4204,7 +4204,7 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -4222,7 +4222,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -4251,10 +4251,10 @@
         <v>93.3</v>
       </c>
       <c r="H7">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -4266,13 +4266,13 @@
         <v>96</v>
       </c>
       <c r="M7">
-        <v>93.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N7">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -4284,7 +4284,7 @@
         <v>96</v>
       </c>
       <c r="S7">
-        <v>93.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4369,7 +4369,7 @@
         <v>90</v>
       </c>
       <c r="H9">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -4381,13 +4381,13 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M9">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="N9">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -4399,10 +4399,10 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="S9">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4487,7 +4487,7 @@
         <v>93.3</v>
       </c>
       <c r="H11">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -4502,10 +4502,10 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="N11">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -4520,7 +4520,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>93.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4549,7 +4549,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4558,7 +4558,7 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -4567,7 +4567,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -4576,7 +4576,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -4608,7 +4608,7 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -4617,7 +4617,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -4626,7 +4626,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -4635,7 +4635,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4723,10 +4723,10 @@
         <v>93.3</v>
       </c>
       <c r="H15">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I15">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4738,13 +4738,13 @@
         <v>100</v>
       </c>
       <c r="M15">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N15">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O15">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -4756,7 +4756,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4782,10 +4782,10 @@
         <v>90</v>
       </c>
       <c r="H16">
-        <v>90</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I16">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -4794,16 +4794,16 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M16">
-        <v>90</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N16">
-        <v>90</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O16">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4812,10 +4812,10 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S16">
-        <v>90</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4900,7 +4900,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I18">
         <v>90</v>
@@ -4912,13 +4912,13 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O18">
         <v>90</v>
@@ -4930,10 +4930,10 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4959,40 +4959,40 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I19">
         <v>95</v>
       </c>
       <c r="J19">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O19">
         <v>95</v>
       </c>
       <c r="P19">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -5018,40 +5018,40 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="I20">
         <v>100</v>
       </c>
       <c r="J20">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -5080,7 +5080,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -5089,7 +5089,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -5098,7 +5098,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -5107,7 +5107,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -5136,13 +5136,13 @@
         <v>93.3</v>
       </c>
       <c r="H22">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I22">
         <v>95</v>
       </c>
       <c r="J22">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -5151,16 +5151,16 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N22">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O22">
         <v>95</v>
       </c>
       <c r="P22">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -5169,7 +5169,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -5195,13 +5195,13 @@
         <v>90</v>
       </c>
       <c r="H23">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="I23">
+        <v>85</v>
+      </c>
+      <c r="J23">
         <v>90</v>
-      </c>
-      <c r="I23">
-        <v>75</v>
-      </c>
-      <c r="J23">
-        <v>80</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -5210,16 +5210,16 @@
         <v>96</v>
       </c>
       <c r="M23">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="N23">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="O23">
+        <v>85</v>
+      </c>
+      <c r="P23">
         <v>90</v>
-      </c>
-      <c r="N23">
-        <v>90</v>
-      </c>
-      <c r="O23">
-        <v>75</v>
-      </c>
-      <c r="P23">
-        <v>80</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5228,7 +5228,7 @@
         <v>96</v>
       </c>
       <c r="S23">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5257,7 +5257,7 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -5266,7 +5266,7 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -5275,7 +5275,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5284,7 +5284,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -5328,7 +5328,7 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="N25">
         <v>100</v>
@@ -5346,7 +5346,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5375,16 +5375,16 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -5393,16 +5393,16 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -5431,40 +5431,40 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I27">
         <v>95</v>
       </c>
       <c r="J27">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O27">
         <v>95</v>
       </c>
       <c r="P27">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q27">
         <v>100</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5549,40 +5549,40 @@
         <v>83.3</v>
       </c>
       <c r="H29">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I29">
-        <v>65</v>
+        <v>82.5</v>
       </c>
       <c r="J29">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
+        <v>90</v>
+      </c>
+      <c r="M29">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="N29">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="O29">
+        <v>82.5</v>
+      </c>
+      <c r="P29">
         <v>88</v>
       </c>
-      <c r="M29">
-        <v>83.3</v>
-      </c>
-      <c r="N29">
-        <v>83.3</v>
-      </c>
-      <c r="O29">
-        <v>65</v>
-      </c>
-      <c r="P29">
-        <v>76</v>
-      </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="S29">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5608,40 +5608,40 @@
         <v>90</v>
       </c>
       <c r="H30">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I30">
-        <v>65</v>
+        <v>82.5</v>
       </c>
       <c r="J30">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M30">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="N30">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O30">
-        <v>65</v>
+        <v>82.5</v>
       </c>
       <c r="P30">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="Q30">
         <v>100</v>
       </c>
       <c r="R30">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S30">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5788,10 +5788,10 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J33">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -5806,10 +5806,10 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P33">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -5903,40 +5903,40 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J35">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K35">
         <v>100</v>
       </c>
       <c r="L35">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N35">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P35">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q35">
         <v>100</v>
       </c>
       <c r="R35">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -6021,40 +6021,40 @@
         <v>83.3</v>
       </c>
       <c r="H37">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I37">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="J37">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="K37">
         <v>78.3</v>
       </c>
       <c r="L37">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M37">
-        <v>83.3</v>
+        <v>84.8</v>
       </c>
       <c r="N37">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O37">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="P37">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="Q37">
         <v>78.3</v>
       </c>
       <c r="R37">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S37">
-        <v>83.3</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -6092,7 +6092,7 @@
         <v>100</v>
       </c>
       <c r="L38">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M38">
         <v>100</v>
@@ -6110,7 +6110,7 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S38">
         <v>100</v>
@@ -6142,7 +6142,7 @@
         <v>100</v>
       </c>
       <c r="I39">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J39">
         <v>100</v>
@@ -6151,7 +6151,7 @@
         <v>100</v>
       </c>
       <c r="L39">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M39">
         <v>100</v>
@@ -6160,7 +6160,7 @@
         <v>100</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P39">
         <v>100</v>
@@ -6169,7 +6169,7 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S39">
         <v>100</v>
@@ -6201,10 +6201,10 @@
         <v>100</v>
       </c>
       <c r="I40">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J40">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K40">
         <v>100</v>
@@ -6219,10 +6219,10 @@
         <v>100</v>
       </c>
       <c r="O40">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P40">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -6269,7 +6269,7 @@
         <v>100</v>
       </c>
       <c r="L41">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M41">
         <v>100</v>
@@ -6287,7 +6287,7 @@
         <v>100</v>
       </c>
       <c r="R41">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S41">
         <v>100</v>
@@ -6322,7 +6322,7 @@
         <v>90</v>
       </c>
       <c r="J42">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K42">
         <v>100</v>
@@ -6340,7 +6340,7 @@
         <v>90</v>
       </c>
       <c r="P42">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q42">
         <v>100</v>
@@ -6375,10 +6375,10 @@
         <v>93.3</v>
       </c>
       <c r="H43">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="I43">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J43">
         <v>100</v>
@@ -6387,16 +6387,16 @@
         <v>100</v>
       </c>
       <c r="L43">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M43">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="N43">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="O43">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P43">
         <v>100</v>
@@ -6405,10 +6405,10 @@
         <v>100</v>
       </c>
       <c r="R43">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S43">
-        <v>93.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -6437,7 +6437,7 @@
         <v>100</v>
       </c>
       <c r="I44">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J44">
         <v>100</v>
@@ -6446,7 +6446,7 @@
         <v>100</v>
       </c>
       <c r="L44">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M44">
         <v>100</v>
@@ -6455,7 +6455,7 @@
         <v>100</v>
       </c>
       <c r="O44">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P44">
         <v>100</v>
@@ -6464,7 +6464,7 @@
         <v>100</v>
       </c>
       <c r="R44">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S44">
         <v>100</v>
@@ -6565,19 +6565,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>92.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>7.3</v>
+        <v>4.9</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6609,7 +6609,7 @@
         <v>2.4</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6641,7 +6641,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6755,7 +6755,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6799,10 +6799,10 @@
         <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6810,16 +6810,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920339</v>
+        <v>22330051920098</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -6833,16 +6833,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920340</v>
+        <v>22330051920116</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -6856,22 +6856,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920100</v>
+        <v>22330051920116</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6879,22 +6879,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920105</v>
+        <v>22330051920339</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6902,16 +6902,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920108</v>
+        <v>22330051920340</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -6925,24 +6925,70 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920107</v>
+        <v>22330051920105</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
         <v>85</v>
       </c>
       <c r="D8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920108</v>
+      </c>
+      <c r="B9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920107</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" t="s">
         <v>93</v>
       </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
         <v>65</v>
       </c>
-      <c r="G8">
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCM - Estadisticos 20241.xlsx
+++ b/grupos/5ALCM - Estadisticos 20241.xlsx
@@ -215,10 +215,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
+    <t>Martínez Sota Luis Rey</t>
+  </si>
+  <si>
+    <t>Diaz Rodriguez Aurelio</t>
   </si>
   <si>
     <t>Ramírez Vargas Miranda Alejandra</t>

--- a/grupos/5ALCM - Estadisticos 20241.xlsx
+++ b/grupos/5ALCM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="89">
   <si>
     <t>Materia</t>
   </si>
@@ -242,64 +242,49 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>JALAPA</t>
   </si>
   <si>
-    <t>LARRACILLA</t>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
+    <t>SOTO</t>
   </si>
   <si>
     <t>PRADO</t>
   </si>
   <si>
-    <t>SOTO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>GOMEZ</t>
+    <t>LUGO</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
+    <t>ANDRES</t>
   </si>
   <si>
     <t>ANETTE</t>
   </si>
   <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
     <t>JAZMIN</t>
   </si>
   <si>
-    <t>MONSERRAT</t>
+    <t>ZAYRA</t>
   </si>
   <si>
     <t>VALERIA</t>
-  </si>
-  <si>
-    <t>BARUCH BOSET</t>
-  </si>
-  <si>
-    <t>AHILY</t>
   </si>
 </sst>
 </file>
@@ -816,7 +801,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -852,7 +837,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -893,7 +878,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>9</v>
@@ -929,7 +914,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -970,7 +955,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -1006,7 +991,7 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1047,7 +1032,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -1083,7 +1068,7 @@
         <v>10</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1124,7 +1109,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -1160,7 +1145,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1201,7 +1186,7 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -1278,7 +1263,7 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1314,7 +1299,7 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1355,7 +1340,7 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -1391,7 +1376,7 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1432,7 +1417,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -1468,7 +1453,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1509,7 +1494,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>9</v>
@@ -1545,7 +1530,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1586,7 +1571,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>8</v>
@@ -1622,7 +1607,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -1663,7 +1648,7 @@
         <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>8</v>
@@ -1699,7 +1684,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1740,7 +1725,7 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -1776,7 +1761,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -1817,7 +1802,7 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>7</v>
@@ -1853,7 +1838,7 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -1894,7 +1879,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -1930,7 +1915,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -1971,7 +1956,7 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>6</v>
@@ -2007,7 +1992,7 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -2048,7 +2033,7 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -2125,7 +2110,7 @@
         <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -2161,7 +2146,7 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2202,7 +2187,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>8</v>
@@ -2238,7 +2223,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2279,7 +2264,7 @@
         <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>7</v>
@@ -2315,7 +2300,7 @@
         <v>6</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2356,7 +2341,7 @@
         <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -2433,7 +2418,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2510,7 +2495,7 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>8</v>
@@ -2546,7 +2531,7 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2587,7 +2572,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>6</v>
@@ -2623,7 +2608,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -2664,7 +2649,7 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -2741,7 +2726,7 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>7</v>
@@ -2777,7 +2762,7 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -2818,7 +2803,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>8</v>
@@ -2854,7 +2839,7 @@
         <v>9</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -2895,7 +2880,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>9</v>
@@ -2972,7 +2957,7 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>7</v>
@@ -3008,7 +2993,7 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -3049,7 +3034,7 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>8</v>
@@ -3085,7 +3070,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3126,7 +3111,7 @@
         <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>9</v>
@@ -3203,7 +3188,7 @@
         <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>8</v>
@@ -3239,7 +3224,7 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>8</v>
@@ -3280,7 +3265,7 @@
         <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -3316,7 +3301,7 @@
         <v>10</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3357,7 +3342,7 @@
         <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L37">
         <v>7</v>
@@ -3434,7 +3419,7 @@
         <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
         <v>10</v>
@@ -3511,7 +3496,7 @@
         <v>9</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L39">
         <v>9</v>
@@ -3547,7 +3532,7 @@
         <v>10</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>10</v>
@@ -3588,7 +3573,7 @@
         <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L40">
         <v>8</v>
@@ -3624,7 +3609,7 @@
         <v>9</v>
       </c>
       <c r="W40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>9</v>
@@ -3665,7 +3650,7 @@
         <v>10</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L41">
         <v>10</v>
@@ -3742,7 +3727,7 @@
         <v>9</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L42">
         <v>8</v>
@@ -3778,7 +3763,7 @@
         <v>9</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X42">
         <v>9</v>
@@ -3819,7 +3804,7 @@
         <v>10</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L43">
         <v>7</v>
@@ -3855,7 +3840,7 @@
         <v>10</v>
       </c>
       <c r="W43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X43">
         <v>9</v>
@@ -3896,7 +3881,7 @@
         <v>10</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L44">
         <v>10</v>
@@ -5204,7 +5189,7 @@
         <v>90</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L23">
         <v>96</v>
@@ -5222,7 +5207,7 @@
         <v>90</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="R23">
         <v>96</v>
@@ -6030,7 +6015,7 @@
         <v>86</v>
       </c>
       <c r="K37">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="L37">
         <v>80</v>
@@ -6048,7 +6033,7 @@
         <v>86</v>
       </c>
       <c r="Q37">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="R37">
         <v>80</v>
@@ -6533,19 +6518,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>85.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="G2" s="2">
-        <v>14.6</v>
+        <v>7.3</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6755,7 +6740,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6787,22 +6772,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920098</v>
+        <v>22330051920116</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6810,22 +6795,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920098</v>
+        <v>22330051920116</v>
       </c>
       <c r="B3" t="s">
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6833,22 +6818,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920116</v>
+        <v>22330051920098</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6856,22 +6841,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920116</v>
+        <v>22330051920339</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6879,16 +6864,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920339</v>
+        <v>22330051920100</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6902,93 +6887,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920340</v>
+        <v>22330051920105</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920105</v>
-      </c>
-      <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920108</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920107</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCM - Estadisticos 20241.xlsx
+++ b/grupos/5ALCM - Estadisticos 20241.xlsx
@@ -810,13 +810,13 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -825,7 +825,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -887,13 +887,13 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -902,7 +902,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -964,13 +964,13 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -979,7 +979,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1041,13 +1041,13 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1056,7 +1056,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1065,7 +1065,7 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1118,13 +1118,13 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1133,7 +1133,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1195,13 +1195,13 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1210,7 +1210,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1272,13 +1272,13 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1287,7 +1287,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1349,13 +1349,13 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1364,7 +1364,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1373,7 +1373,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1426,13 +1426,13 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1441,7 +1441,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>10</v>
@@ -1503,13 +1503,13 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1518,13 +1518,13 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1580,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1595,7 +1595,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1657,13 +1657,13 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1672,7 +1672,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1734,13 +1734,13 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -1749,7 +1749,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1758,7 +1758,7 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1811,13 +1811,13 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -1826,7 +1826,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -1888,13 +1888,13 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -1903,10 +1903,10 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -1921,7 +1921,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1965,13 +1965,13 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -1980,16 +1980,16 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>5</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -1998,7 +1998,7 @@
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2042,13 +2042,13 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2057,16 +2057,16 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>7</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2075,7 +2075,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2119,13 +2119,13 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2134,7 +2134,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2196,13 +2196,13 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2211,7 +2211,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2220,7 +2220,7 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2273,13 +2273,13 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2288,10 +2288,10 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>7</v>
@@ -2306,7 +2306,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2350,13 +2350,13 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2365,7 +2365,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2412,7 +2412,7 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>10</v>
@@ -2427,13 +2427,13 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2442,13 +2442,13 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2504,13 +2504,13 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2519,7 +2519,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2581,13 +2581,13 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2596,10 +2596,10 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>5</v>
@@ -2614,7 +2614,7 @@
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2658,13 +2658,13 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2673,7 +2673,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2735,13 +2735,13 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -2750,7 +2750,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -2759,7 +2759,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -2812,13 +2812,13 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -2827,7 +2827,7 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>8</v>
@@ -2836,7 +2836,7 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -2889,13 +2889,13 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -2904,7 +2904,7 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -2966,13 +2966,13 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -2981,7 +2981,7 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3043,13 +3043,13 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3058,7 +3058,7 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3067,7 +3067,7 @@
         <v>9</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3120,13 +3120,13 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3135,7 +3135,7 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3197,13 +3197,13 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3212,10 +3212,10 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -3230,7 +3230,7 @@
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3274,13 +3274,13 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3289,7 +3289,7 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3351,13 +3351,13 @@
         <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3366,7 +3366,7 @@
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T37">
         <v>7</v>
@@ -3428,13 +3428,13 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -3443,7 +3443,7 @@
         <v>-1</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -3505,13 +3505,13 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -3520,7 +3520,7 @@
         <v>-1</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -3529,7 +3529,7 @@
         <v>9</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W39">
         <v>8</v>
@@ -3582,13 +3582,13 @@
         <v>10</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -3597,7 +3597,7 @@
         <v>-1</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
         <v>10</v>
@@ -3659,13 +3659,13 @@
         <v>10</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O41">
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -3674,7 +3674,7 @@
         <v>-1</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
         <v>10</v>
@@ -3736,13 +3736,13 @@
         <v>10</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O42">
         <v>-1</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -3751,7 +3751,7 @@
         <v>-1</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
         <v>10</v>
@@ -3813,13 +3813,13 @@
         <v>10</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O43">
         <v>-1</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -3828,7 +3828,7 @@
         <v>-1</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T43">
         <v>10</v>
@@ -3890,13 +3890,13 @@
         <v>10</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O44">
         <v>-1</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q44">
         <v>-1</v>
@@ -3905,7 +3905,7 @@
         <v>-1</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T44">
         <v>10</v>
@@ -4254,7 +4254,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N7">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="O7">
         <v>97.5</v>
@@ -4269,7 +4269,7 @@
         <v>96</v>
       </c>
       <c r="S7">
-        <v>90.90000000000001</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4313,7 +4313,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -4328,7 +4328,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4372,7 +4372,7 @@
         <v>89.40000000000001</v>
       </c>
       <c r="N9">
-        <v>89.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -4387,7 +4387,7 @@
         <v>92</v>
       </c>
       <c r="S9">
-        <v>89.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4490,7 +4490,7 @@
         <v>97</v>
       </c>
       <c r="N11">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -4505,7 +4505,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4667,7 +4667,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -4682,7 +4682,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4726,7 +4726,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N15">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="O15">
         <v>92.5</v>
@@ -4741,7 +4741,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4785,7 +4785,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N16">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="O16">
         <v>85</v>
@@ -4800,7 +4800,7 @@
         <v>98</v>
       </c>
       <c r="S16">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4903,7 +4903,7 @@
         <v>97</v>
       </c>
       <c r="N18">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="O18">
         <v>90</v>
@@ -4918,7 +4918,7 @@
         <v>96</v>
       </c>
       <c r="S18">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4962,13 +4962,13 @@
         <v>98.5</v>
       </c>
       <c r="N19">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="O19">
         <v>95</v>
       </c>
       <c r="P19">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4977,7 +4977,7 @@
         <v>94</v>
       </c>
       <c r="S19">
-        <v>98.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -5021,13 +5021,13 @@
         <v>97</v>
       </c>
       <c r="N20">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -5036,7 +5036,7 @@
         <v>96</v>
       </c>
       <c r="S20">
-        <v>97</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -5139,13 +5139,13 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N22">
-        <v>93.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="O22">
         <v>95</v>
       </c>
       <c r="P22">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -5154,7 +5154,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -5198,13 +5198,13 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N23">
-        <v>89.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="O23">
         <v>85</v>
       </c>
       <c r="P23">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q23">
         <v>97.7</v>
@@ -5213,7 +5213,7 @@
         <v>96</v>
       </c>
       <c r="S23">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5331,7 +5331,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5381,7 +5381,7 @@
         <v>97.5</v>
       </c>
       <c r="P26">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5434,13 +5434,13 @@
         <v>98.5</v>
       </c>
       <c r="N27">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="O27">
         <v>95</v>
       </c>
       <c r="P27">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5449,7 +5449,7 @@
         <v>98</v>
       </c>
       <c r="S27">
-        <v>98.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5552,13 +5552,13 @@
         <v>86.40000000000001</v>
       </c>
       <c r="N29">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="O29">
         <v>82.5</v>
       </c>
       <c r="P29">
-        <v>88</v>
+        <v>92.5</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5567,7 +5567,7 @@
         <v>90</v>
       </c>
       <c r="S29">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5611,13 +5611,13 @@
         <v>89.40000000000001</v>
       </c>
       <c r="N30">
-        <v>89.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="O30">
         <v>82.5</v>
       </c>
       <c r="P30">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5626,7 +5626,7 @@
         <v>94</v>
       </c>
       <c r="S30">
-        <v>89.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5794,7 +5794,7 @@
         <v>95</v>
       </c>
       <c r="P33">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -5906,13 +5906,13 @@
         <v>97</v>
       </c>
       <c r="N35">
-        <v>97</v>
+        <v>94.8</v>
       </c>
       <c r="O35">
         <v>95</v>
       </c>
       <c r="P35">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -5921,7 +5921,7 @@
         <v>94</v>
       </c>
       <c r="S35">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -6024,13 +6024,13 @@
         <v>84.8</v>
       </c>
       <c r="N37">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="O37">
         <v>70</v>
       </c>
       <c r="P37">
-        <v>86</v>
+        <v>91.3</v>
       </c>
       <c r="Q37">
         <v>86</v>
@@ -6039,7 +6039,7 @@
         <v>80</v>
       </c>
       <c r="S37">
-        <v>84.8</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -6207,7 +6207,7 @@
         <v>97.5</v>
       </c>
       <c r="P40">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -6325,7 +6325,7 @@
         <v>90</v>
       </c>
       <c r="P42">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q42">
         <v>100</v>
@@ -6378,7 +6378,7 @@
         <v>97</v>
       </c>
       <c r="N43">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="O43">
         <v>95</v>
@@ -6393,7 +6393,7 @@
         <v>98</v>
       </c>
       <c r="S43">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -6562,7 +6562,7 @@
         <v>4.9</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6626,7 +6626,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6658,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5ALCM - Estadisticos 20241.xlsx
+++ b/grupos/5ALCM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -242,49 +242,31 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>JALAPA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JALAPA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>LUGO</t>
   </si>
   <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LUGO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
   </si>
   <si>
     <t>ANDRES</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
   </si>
 </sst>
 </file>
@@ -813,16 +795,16 @@
         <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>10</v>
@@ -890,16 +872,16 @@
         <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -967,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>10</v>
@@ -991,7 +973,7 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1044,16 +1026,16 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>10</v>
@@ -1121,16 +1103,16 @@
         <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>9</v>
@@ -1148,7 +1130,7 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1198,16 +1180,16 @@
         <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -1275,16 +1257,16 @@
         <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>10</v>
@@ -1352,16 +1334,16 @@
         <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>10</v>
@@ -1376,7 +1358,7 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1429,16 +1411,16 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>10</v>
@@ -1506,16 +1488,16 @@
         <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
         <v>10</v>
@@ -1583,16 +1565,16 @@
         <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>10</v>
@@ -1660,16 +1642,16 @@
         <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>9</v>
@@ -1737,16 +1719,16 @@
         <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>10</v>
@@ -1761,7 +1743,7 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -1814,16 +1796,16 @@
         <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>10</v>
@@ -1891,16 +1873,16 @@
         <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>9</v>
@@ -1909,7 +1891,7 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -1968,16 +1950,16 @@
         <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>9</v>
@@ -1986,13 +1968,13 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>8</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -2045,16 +2027,16 @@
         <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>6</v>
@@ -2063,7 +2045,7 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2072,7 +2054,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2122,16 +2104,16 @@
         <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
         <v>10</v>
@@ -2149,7 +2131,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2199,16 +2181,16 @@
         <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
         <v>8</v>
@@ -2217,7 +2199,7 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2276,16 +2258,16 @@
         <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
         <v>7</v>
@@ -2303,7 +2285,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2353,16 +2335,16 @@
         <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>10</v>
@@ -2377,7 +2359,7 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2430,16 +2412,16 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>10</v>
@@ -2507,16 +2489,16 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>10</v>
@@ -2584,16 +2566,16 @@
         <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>9</v>
@@ -2602,7 +2584,7 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -2661,16 +2643,16 @@
         <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>10</v>
@@ -2738,16 +2720,16 @@
         <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
         <v>7</v>
@@ -2756,7 +2738,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2765,7 +2747,7 @@
         <v>6</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2815,16 +2797,16 @@
         <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
         <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>8</v>
@@ -2842,7 +2824,7 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -2892,16 +2874,16 @@
         <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>10</v>
@@ -2916,7 +2898,7 @@
         <v>10</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -2969,16 +2951,16 @@
         <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
         <v>10</v>
@@ -3046,16 +3028,16 @@
         <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>10</v>
@@ -3070,7 +3052,7 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3123,16 +3105,16 @@
         <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>10</v>
@@ -3147,7 +3129,7 @@
         <v>10</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3200,16 +3182,16 @@
         <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
         <v>9</v>
@@ -3277,16 +3259,16 @@
         <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
         <v>10</v>
@@ -3354,16 +3336,16 @@
         <v>6</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
         <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
         <v>6</v>
@@ -3372,16 +3354,16 @@
         <v>7</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V37">
         <v>6</v>
       </c>
       <c r="W37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>7</v>
@@ -3431,16 +3413,16 @@
         <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
         <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
         <v>10</v>
@@ -3508,16 +3490,16 @@
         <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
         <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
         <v>10</v>
@@ -3585,16 +3567,16 @@
         <v>10</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
         <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
         <v>10</v>
@@ -3612,7 +3594,7 @@
         <v>8</v>
       </c>
       <c r="X40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y40">
         <v>10</v>
@@ -3662,16 +3644,16 @@
         <v>10</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P41">
         <v>10</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
         <v>10</v>
@@ -3739,16 +3721,16 @@
         <v>10</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P42">
         <v>9</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S42">
         <v>10</v>
@@ -3816,16 +3798,16 @@
         <v>10</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P43">
         <v>10</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S43">
         <v>10</v>
@@ -3834,7 +3816,7 @@
         <v>10</v>
       </c>
       <c r="U43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V43">
         <v>10</v>
@@ -3893,16 +3875,16 @@
         <v>10</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P44">
         <v>10</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S44">
         <v>10</v>
@@ -3917,7 +3899,7 @@
         <v>10</v>
       </c>
       <c r="W44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X44">
         <v>10</v>
@@ -4080,13 +4062,13 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -4207,7 +4189,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -4257,16 +4239,16 @@
         <v>92.7</v>
       </c>
       <c r="O7">
+        <v>96.7</v>
+      </c>
+      <c r="P7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
         <v>97.5</v>
-      </c>
-      <c r="P7">
-        <v>100</v>
-      </c>
-      <c r="Q7">
-        <v>100</v>
-      </c>
-      <c r="R7">
-        <v>96</v>
       </c>
       <c r="S7">
         <v>91.7</v>
@@ -4316,7 +4298,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -4325,7 +4307,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S8">
         <v>97.90000000000001</v>
@@ -4384,7 +4366,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S9">
         <v>90.59999999999999</v>
@@ -4499,7 +4481,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -4552,16 +4534,16 @@
         <v>100</v>
       </c>
       <c r="O12">
+        <v>98.3</v>
+      </c>
+      <c r="P12">
+        <v>100</v>
+      </c>
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
         <v>97.5</v>
-      </c>
-      <c r="P12">
-        <v>100</v>
-      </c>
-      <c r="Q12">
-        <v>100</v>
-      </c>
-      <c r="R12">
-        <v>96</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -4611,16 +4593,16 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R13">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4729,16 +4711,16 @@
         <v>93.8</v>
       </c>
       <c r="O15">
+        <v>93.3</v>
+      </c>
+      <c r="P15">
+        <v>100</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
         <v>92.5</v>
-      </c>
-      <c r="P15">
-        <v>100</v>
-      </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
-      <c r="R15">
-        <v>100</v>
       </c>
       <c r="S15">
         <v>93.8</v>
@@ -4788,7 +4770,7 @@
         <v>93.8</v>
       </c>
       <c r="O16">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4797,7 +4779,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="S16">
         <v>93.8</v>
@@ -4847,7 +4829,7 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4915,7 +4897,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>96</v>
+        <v>91.3</v>
       </c>
       <c r="S18">
         <v>95.8</v>
@@ -4971,10 +4953,10 @@
         <v>98.8</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R19">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S19">
         <v>96.90000000000001</v>
@@ -5024,16 +5006,16 @@
         <v>92.7</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P20">
         <v>97.5</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R20">
-        <v>96</v>
+        <v>93.8</v>
       </c>
       <c r="S20">
         <v>93.8</v>
@@ -5083,7 +5065,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -5092,7 +5074,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -5151,7 +5133,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S22">
         <v>93.8</v>
@@ -5201,16 +5183,16 @@
         <v>88.5</v>
       </c>
       <c r="O23">
-        <v>85</v>
+        <v>86.7</v>
       </c>
       <c r="P23">
         <v>93.8</v>
       </c>
       <c r="Q23">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="R23">
-        <v>96</v>
+        <v>86.3</v>
       </c>
       <c r="S23">
         <v>90.59999999999999</v>
@@ -5260,7 +5242,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5269,7 +5251,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -5378,7 +5360,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="P26">
         <v>93.8</v>
@@ -5387,7 +5369,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>98</v>
+        <v>93.8</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -5437,7 +5419,7 @@
         <v>95.8</v>
       </c>
       <c r="O27">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="P27">
         <v>98.8</v>
@@ -5446,7 +5428,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>98</v>
+        <v>92.5</v>
       </c>
       <c r="S27">
         <v>96.90000000000001</v>
@@ -5496,7 +5478,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -5555,7 +5537,7 @@
         <v>86.5</v>
       </c>
       <c r="O29">
-        <v>82.5</v>
+        <v>86.7</v>
       </c>
       <c r="P29">
         <v>92.5</v>
@@ -5564,7 +5546,7 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="S29">
         <v>86.5</v>
@@ -5614,7 +5596,7 @@
         <v>89.59999999999999</v>
       </c>
       <c r="O30">
-        <v>82.5</v>
+        <v>86.7</v>
       </c>
       <c r="P30">
         <v>95</v>
@@ -5623,7 +5605,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>94</v>
+        <v>91.3</v>
       </c>
       <c r="S30">
         <v>89.59999999999999</v>
@@ -5682,7 +5664,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -5741,7 +5723,7 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -5800,7 +5782,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -5856,10 +5838,10 @@
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S34">
         <v>100</v>
@@ -5918,7 +5900,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="S35">
         <v>95.8</v>
@@ -5968,7 +5950,7 @@
         <v>100</v>
       </c>
       <c r="O36">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P36">
         <v>100</v>
@@ -6027,16 +6009,16 @@
         <v>86.5</v>
       </c>
       <c r="O37">
-        <v>70</v>
+        <v>78.3</v>
       </c>
       <c r="P37">
         <v>91.3</v>
       </c>
       <c r="Q37">
-        <v>86</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R37">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="S37">
         <v>85.40000000000001</v>
@@ -6092,10 +6074,10 @@
         <v>100</v>
       </c>
       <c r="Q38">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R38">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="S38">
         <v>100</v>
@@ -6145,16 +6127,16 @@
         <v>100</v>
       </c>
       <c r="O39">
+        <v>98.3</v>
+      </c>
+      <c r="P39">
+        <v>100</v>
+      </c>
+      <c r="Q39">
+        <v>100</v>
+      </c>
+      <c r="R39">
         <v>97.5</v>
-      </c>
-      <c r="P39">
-        <v>100</v>
-      </c>
-      <c r="Q39">
-        <v>100</v>
-      </c>
-      <c r="R39">
-        <v>98</v>
       </c>
       <c r="S39">
         <v>100</v>
@@ -6204,7 +6186,7 @@
         <v>100</v>
       </c>
       <c r="O40">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="P40">
         <v>97.5</v>
@@ -6272,7 +6254,7 @@
         <v>100</v>
       </c>
       <c r="R41">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="S41">
         <v>100</v>
@@ -6331,7 +6313,7 @@
         <v>100</v>
       </c>
       <c r="R42">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="S42">
         <v>100</v>
@@ -6381,7 +6363,7 @@
         <v>95.8</v>
       </c>
       <c r="O43">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="P43">
         <v>100</v>
@@ -6390,7 +6372,7 @@
         <v>100</v>
       </c>
       <c r="R43">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="S43">
         <v>95.8</v>
@@ -6440,16 +6422,16 @@
         <v>100</v>
       </c>
       <c r="O44">
+        <v>98.3</v>
+      </c>
+      <c r="P44">
+        <v>100</v>
+      </c>
+      <c r="Q44">
+        <v>100</v>
+      </c>
+      <c r="R44">
         <v>97.5</v>
-      </c>
-      <c r="P44">
-        <v>100</v>
-      </c>
-      <c r="Q44">
-        <v>100</v>
-      </c>
-      <c r="R44">
-        <v>98</v>
       </c>
       <c r="S44">
         <v>100</v>
@@ -6518,19 +6500,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>92.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>7.3</v>
+        <v>4.9</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6550,19 +6532,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>95.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6582,19 +6564,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6740,7 +6722,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6772,16 +6754,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920116</v>
+        <v>22330051920339</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6795,22 +6777,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920116</v>
+        <v>22330051920100</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6818,16 +6800,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920098</v>
+        <v>22330051920116</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6836,75 +6818,6 @@
         <v>66</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920339</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920100</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920105</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>
